--- a/alquiler_de_UPS.xlsx
+++ b/alquiler_de_UPS.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="62">
   <si>
     <t>COTIZACION</t>
   </si>
@@ -205,9 +205,6 @@
   </si>
   <si>
     <t>EVENTO COLEGIO SAN SILVESTRE</t>
-  </si>
-  <si>
-    <t>STB 22</t>
   </si>
 </sst>
 </file>
@@ -567,7 +564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" customWidth="1"/>
@@ -971,32 +968,6 @@
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" s="1">
-        <v>2026</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F16" s="1">
-        <v>2</v>
-      </c>
-      <c r="G16" s="1">
-        <v>100</v>
-      </c>
-      <c r="H16" s="1">
-        <v>200</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/alquiler_de_UPS.xlsx
+++ b/alquiler_de_UPS.xlsx
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="88">
   <si>
     <t>COTIZACION</t>
   </si>
@@ -205,6 +205,84 @@
   </si>
   <si>
     <t>EVENTO COLEGIO SAN SILVESTRE</t>
+  </si>
+  <si>
+    <t>110926-01</t>
+  </si>
+  <si>
+    <t>SBUX 61</t>
+  </si>
+  <si>
+    <t>12 DE SETIEMBRE</t>
+  </si>
+  <si>
+    <t>EMBAJADA DE USA</t>
+  </si>
+  <si>
+    <t>110926-02</t>
+  </si>
+  <si>
+    <t>PHD 04</t>
+  </si>
+  <si>
+    <t>110926-03</t>
+  </si>
+  <si>
+    <t>SBUX 87</t>
+  </si>
+  <si>
+    <t>COLEGIO CHAMPAGNAT</t>
+  </si>
+  <si>
+    <t>170926-01</t>
+  </si>
+  <si>
+    <t>SBUX 94</t>
+  </si>
+  <si>
+    <t>17 Y 18 DE SETIEMBRE</t>
+  </si>
+  <si>
+    <t>170926-02</t>
+  </si>
+  <si>
+    <t>PB 24</t>
+  </si>
+  <si>
+    <t>18 Y 18 DE SETIEMBRE</t>
+  </si>
+  <si>
+    <t>180926-02</t>
+  </si>
+  <si>
+    <t>KFC 85</t>
+  </si>
+  <si>
+    <t>21 AL 25 DE SETIEMBRE</t>
+  </si>
+  <si>
+    <t>UPC - SEMANA UNIVERSITARIA</t>
+  </si>
+  <si>
+    <t>180926-03</t>
+  </si>
+  <si>
+    <t>PT 04</t>
+  </si>
+  <si>
+    <t>26 DE SETIEMBRE</t>
+  </si>
+  <si>
+    <t>COLEGIO GEORGE COLLEGE</t>
+  </si>
+  <si>
+    <t>180926-04</t>
+  </si>
+  <si>
+    <t>SBUX 100</t>
+  </si>
+  <si>
+    <t>COLEGIO CASUARINAS</t>
   </si>
 </sst>
 </file>
@@ -256,10 +334,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -564,408 +642,642 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="36.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="14.42578125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17" style="2" customWidth="1"/>
+    <col min="3" max="3" width="22.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="36.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1">
-        <v>2026</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="D2" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="2">
         <v>1</v>
       </c>
-      <c r="G2" s="1">
-        <v>100</v>
-      </c>
-      <c r="H2" s="1">
+      <c r="G2" s="2">
+        <v>100</v>
+      </c>
+      <c r="H2" s="2">
         <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="1">
-        <v>2026</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="D3" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="2">
         <v>1</v>
       </c>
-      <c r="G3" s="1">
-        <v>100</v>
-      </c>
-      <c r="H3" s="1">
+      <c r="G3" s="2">
+        <v>100</v>
+      </c>
+      <c r="H3" s="2">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="1">
-        <v>2026</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="D4" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="2">
         <v>1</v>
       </c>
-      <c r="G4" s="1">
-        <v>100</v>
-      </c>
-      <c r="H4" s="1">
+      <c r="G4" s="2">
+        <v>100</v>
+      </c>
+      <c r="H4" s="2">
         <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="1">
-        <v>2026</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="D5" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="2">
         <v>2</v>
       </c>
-      <c r="G5" s="1">
-        <v>100</v>
-      </c>
-      <c r="H5" s="1">
+      <c r="G5" s="2">
+        <v>100</v>
+      </c>
+      <c r="H5" s="2">
         <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="1">
-        <v>2026</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="D6" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="2">
         <v>1</v>
       </c>
-      <c r="G6" s="1">
-        <v>100</v>
-      </c>
-      <c r="H6" s="1">
+      <c r="G6" s="2">
+        <v>100</v>
+      </c>
+      <c r="H6" s="2">
         <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="1">
-        <v>2026</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="D7" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="2">
         <v>2</v>
       </c>
-      <c r="G7" s="1">
-        <v>100</v>
-      </c>
-      <c r="H7" s="1">
+      <c r="G7" s="2">
+        <v>100</v>
+      </c>
+      <c r="H7" s="2">
         <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="1">
-        <v>2026</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="D8" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="2">
         <v>1</v>
       </c>
-      <c r="G8" s="1">
-        <v>100</v>
-      </c>
-      <c r="H8" s="1">
+      <c r="G8" s="2">
+        <v>100</v>
+      </c>
+      <c r="H8" s="2">
         <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="1">
-        <v>2026</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="D9" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="2">
         <v>2</v>
       </c>
-      <c r="G9" s="1">
-        <v>100</v>
-      </c>
-      <c r="H9" s="1">
+      <c r="G9" s="2">
+        <v>100</v>
+      </c>
+      <c r="H9" s="2">
         <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="1">
-        <v>2026</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="D10" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="2">
         <v>2</v>
       </c>
-      <c r="G10" s="1">
-        <v>100</v>
-      </c>
-      <c r="H10" s="1">
+      <c r="G10" s="2">
+        <v>100</v>
+      </c>
+      <c r="H10" s="2">
         <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="1">
-        <v>2026</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="D11" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="2">
         <v>2</v>
       </c>
-      <c r="G11" s="1">
-        <v>100</v>
-      </c>
-      <c r="H11" s="1">
+      <c r="G11" s="2">
+        <v>100</v>
+      </c>
+      <c r="H11" s="2">
         <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="1">
-        <v>2026</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="D12" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="2">
         <v>1</v>
       </c>
-      <c r="G12" s="1">
-        <v>100</v>
-      </c>
-      <c r="H12" s="1">
+      <c r="G12" s="2">
+        <v>100</v>
+      </c>
+      <c r="H12" s="2">
         <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="1">
-        <v>2026</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="D13" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="2">
         <v>2</v>
       </c>
-      <c r="G13" s="1">
-        <v>100</v>
-      </c>
-      <c r="H13" s="1">
+      <c r="G13" s="2">
+        <v>100</v>
+      </c>
+      <c r="H13" s="2">
         <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="1">
-        <v>2026</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="D14" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="2">
         <v>9</v>
       </c>
-      <c r="G14" s="1">
-        <v>100</v>
-      </c>
-      <c r="H14" s="1">
+      <c r="G14" s="2">
+        <v>100</v>
+      </c>
+      <c r="H14" s="2">
         <v>900</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="1">
-        <v>2026</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="D15" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="2">
         <v>2</v>
       </c>
-      <c r="G15" s="1">
-        <v>100</v>
-      </c>
-      <c r="H15" s="1">
+      <c r="G15" s="2">
+        <v>100</v>
+      </c>
+      <c r="H15" s="2">
         <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2">
+        <v>100</v>
+      </c>
+      <c r="H16" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2">
+        <v>100</v>
+      </c>
+      <c r="H17" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2">
+        <v>100</v>
+      </c>
+      <c r="H18" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="2">
+        <v>2</v>
+      </c>
+      <c r="G19" s="2">
+        <v>100</v>
+      </c>
+      <c r="H19" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="2">
+        <v>2</v>
+      </c>
+      <c r="G20" s="2">
+        <v>100</v>
+      </c>
+      <c r="H20" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D21" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F21" s="2">
+        <v>5</v>
+      </c>
+      <c r="G21" s="2">
+        <v>100</v>
+      </c>
+      <c r="H21" s="2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22" s="2">
+        <v>5</v>
+      </c>
+      <c r="G22" s="2">
+        <v>100</v>
+      </c>
+      <c r="H22" s="2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2">
+        <v>100</v>
+      </c>
+      <c r="H23" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2">
+        <v>100</v>
+      </c>
+      <c r="H24" s="2">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
